--- a/data/trans_bre/IP16A08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 22,63</t>
+          <t>-12,15; 24,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 23,27</t>
+          <t>-7,26; 22,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 38,86</t>
+          <t>-8,44; 40,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 26,33</t>
+          <t>-1,54; 27,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 871,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-98,7; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-46,12; 912,85</t>
+          <t>-48,43; 814,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-62,89; —</t>
+          <t>-64,42; —</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 28,12</t>
+          <t>-9,36; 28,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,92; 2,81</t>
+          <t>-27,33; 2,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 16,69</t>
+          <t>-9,53; 16,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,37; 3,86</t>
+          <t>-31,66; 3,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,49; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-43,41; -1,18</t>
+          <t>-42,76; 1,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 19,15</t>
+          <t>-12,06; 18,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-38,65; 8,17</t>
+          <t>-39,19; 11,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 38,91</t>
+          <t>-5,88; 43,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 54,78</t>
+          <t>-100,0; 73,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 6,84</t>
+          <t>-16,82; 7,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 8,19</t>
+          <t>-13,85; 8,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,02; -2,95</t>
+          <t>-30,96; -2,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 7,62</t>
+          <t>-7,86; 7,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,3; 111,2</t>
+          <t>-85,94; 89,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,17; 72,65</t>
+          <t>-61,2; 77,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-85,91; -8,78</t>
+          <t>-86,49; -2,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,0; 273,87</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 35,37</t>
+          <t>-2,09; 32,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 24,09</t>
+          <t>-8,46; 24,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 35,24</t>
+          <t>7,4; 33,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 9,85</t>
+          <t>-19,79; 9,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,02; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 487,16</t>
+          <t>-54,86; 555,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-85,49; 141,82</t>
+          <t>-81,19; 127,34</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 56,31</t>
+          <t>-19,52; 52,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 0,0</t>
+          <t>-33,23; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 21,07</t>
+          <t>-35,16; 21,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 2,38</t>
+          <t>-39,01; 3,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 398,97</t>
+          <t>-48,42; 403,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 461,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 8,24</t>
+          <t>-7,58; 7,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 5,97</t>
+          <t>-6,94; 6,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 7,44</t>
+          <t>-7,27; 8,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 4,38</t>
+          <t>-7,99; 3,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 66,09</t>
+          <t>-39,32; 68,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,86; 66,51</t>
+          <t>-45,42; 72,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-44,35; 66,52</t>
+          <t>-39,03; 82,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-59,37; 56,87</t>
+          <t>-58,11; 52,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 24,49</t>
+          <t>-12,95; 23,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 22,37</t>
+          <t>-7,71; 21,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 40,91</t>
+          <t>-5,63; 40,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 27,1</t>
+          <t>-0,7; 27,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,43; 814,84</t>
+          <t>-41,89; 851,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-64,42; —</t>
+          <t>-72,46; —</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 28,55</t>
+          <t>-9,42; 29,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 2,78</t>
+          <t>-23,05; 2,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 16,61</t>
+          <t>-9,54; 16,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 3,18</t>
+          <t>-35,35; 3,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,49; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 1,38</t>
+          <t>-44,76; -0,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 18,58</t>
+          <t>-12,02; 19,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-39,19; 11,04</t>
+          <t>-37,88; 7,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 43,12</t>
+          <t>-5,41; 44,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 73,97</t>
+          <t>-100,0; 82,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 7,19</t>
+          <t>-17,75; 5,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 8,22</t>
+          <t>-13,81; 9,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,96; -2,43</t>
+          <t>-31,86; -0,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 7,7</t>
+          <t>-8,42; 8,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,94; 89,49</t>
+          <t>-84,44; 86,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,2; 77,74</t>
+          <t>-63,69; 85,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-86,49; -2,7</t>
+          <t>-87,33; -0,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,09; 367,66</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 32,15</t>
+          <t>-1,4; 31,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 24,86</t>
+          <t>-8,98; 24,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 33,68</t>
+          <t>8,07; 34,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 9,48</t>
+          <t>-20,69; 9,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>-45,6; —</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-53,9; 461,75</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-54,86; 555,14</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-81,19; 127,34</t>
+          <t>-82,88; 110,48</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 52,96</t>
+          <t>-19,28; 52,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 0,0</t>
+          <t>-29,29; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 21,68</t>
+          <t>-36,04; 19,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 3,83</t>
+          <t>-37,67; 2,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,42; 403,42</t>
+          <t>-50,39; 410,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 7,57</t>
+          <t>-7,32; 7,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 6,57</t>
+          <t>-6,65; 6,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 8,27</t>
+          <t>-8,08; 6,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 3,95</t>
+          <t>-8,03; 4,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 68,01</t>
+          <t>-37,9; 62,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-45,42; 72,68</t>
+          <t>-44,48; 69,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 82,41</t>
+          <t>-44,7; 64,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-58,11; 52,84</t>
+          <t>-60,6; 52,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumieron medicamentos para la alergia</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,07</t>
+          <t>12,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>237,38%</t>
+          <t>294,15%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 23,27</t>
+          <t>-13,38; 22,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 21,46</t>
+          <t>-6,98; 23,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 40,29</t>
+          <t>-8,39; 38,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 27,41</t>
+          <t>-0,71; 28,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 871,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-98,7; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,89; 851,7</t>
+          <t>-46,12; 912,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-72,46; —</t>
+          <t>-57,51; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-12,17</t>
+          <t>-12,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-64,57%</t>
+          <t>-63,26%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 29,33</t>
+          <t>-7,19; 28,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 2,89</t>
+          <t>-27,92; 2,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 16,59</t>
+          <t>-9,42; 16,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,35; 3,81</t>
+          <t>-34,28; 4,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,17</t>
+          <t>11,28</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>206,04%</t>
+          <t>176,14%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-44,76; -0,21</t>
+          <t>-43,41; -1,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 19,17</t>
+          <t>-11,97; 19,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 7,87</t>
+          <t>-38,65; 8,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 44,56</t>
+          <t>-10,75; 40,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 82,44</t>
+          <t>-100,0; 54,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 5,94</t>
+          <t>-17,38; 6,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 9,34</t>
+          <t>-15,24; 8,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,86; -0,79</t>
+          <t>-32,02; -2,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 8,53</t>
+          <t>-4,09; 14,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,44; 86,03</t>
+          <t>-82,3; 111,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,69; 85,82</t>
+          <t>-66,17; 72,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-87,33; -0,99</t>
+          <t>-85,91; -8,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,09; 367,66</t>
+          <t>-64,39; 600,54</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,43</t>
+          <t>-3,21</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-31,47%</t>
+          <t>-21,05%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 31,5</t>
+          <t>0,21; 35,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 24,03</t>
+          <t>-9,55; 24,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 34,06</t>
+          <t>7,37; 35,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 9,04</t>
+          <t>-16,9; 13,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,6; —</t>
+          <t>-74,02; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-53,9; 461,75</t>
+          <t>-57,23; 487,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-82,88; 110,48</t>
+          <t>-83,05; 216,21</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-13,32</t>
+          <t>-15,52</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-74,33%</t>
+          <t>-76,74%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 52,23</t>
+          <t>-17,97; 56,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 0,0</t>
+          <t>-32,73; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,04; 19,85</t>
+          <t>-35,34; 21,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 2,97</t>
+          <t>-42,12; 0,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,39; 410,16</t>
+          <t>-43,02; 398,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 461,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-17,67%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 7,84</t>
+          <t>-7,34; 8,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 6,47</t>
+          <t>-6,82; 5,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 6,48</t>
+          <t>-7,93; 7,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 4,19</t>
+          <t>-5,88; 6,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-37,9; 62,62</t>
+          <t>-39,22; 66,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,48; 69,69</t>
+          <t>-44,86; 66,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-44,7; 64,14</t>
+          <t>-44,35; 66,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-60,6; 52,39</t>
+          <t>-43,38; 91,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,173 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,67</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,11</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14,9</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,37</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>91,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>294,15%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.2271368264599258</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.325924785676218</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.034940529465475</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.972252044580897</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1013236803163577</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.8052673413467382</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.135505725767375</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>2.98985901810054</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-13,38; 22,63</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,98; 23,27</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-8,39; 38,86</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-0,71; 28,49</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 871,41</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-98,7; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-46,12; 912,85</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-57,51; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.990076094458876</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.095236977088349</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.468939228985733</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.1269711882000095</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-0.7178343293456434</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.675372580847962</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.113106891611562</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.301254296339629</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.192935939226683</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-6,59</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,6</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-12,65</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>116,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-70,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-63,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-7,19; 28,12</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-27,92; 2,81</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-9,42; 16,69</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-34,28; 4,19</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>2.347844997936997</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.4872742178865664</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.1946231771152998</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-3.20141871347356</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1.319220539702511</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.416276494922315</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.243214629856983</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.6468204045406537</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-25,48</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-13,37</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-77,84%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-67,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>176,14%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.585841743396982</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.804774615101161</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.603892655487187</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-9.290713490649885</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-43,41; -1,18</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-11,97; 19,15</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-38,65; 8,17</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-10,75; 40,26</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 54,78</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.074164108114582</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.372614123708581</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.219856286328099</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.428097042280948</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +793,183 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-5,77</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,24</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-15,94</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,14</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-37,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-18,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-61,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>78,38%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-6.038868687294288</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.06036249596192127</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.77570701837778</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.45796286663947</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.8347128358445656</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.07084915196604527</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.6606513851419896</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.8625391124605277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-17,38; 6,84</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-15,24; 8,19</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-32,02; -2,95</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 14,88</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-82,3; 111,2</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-66,17; 72,65</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-85,91; -8,78</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-64,39; 600,54</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-11.49146530965669</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.593294918231174</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.19093286677905</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.408706522918097</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-1.574722183183364</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.591674880662393</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9954308940687094</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.421282059705968</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.5373671323755044</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>12,91</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6,52</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18,03</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,21</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>239,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>52,21%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-21,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,21; 35,37</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-9,55; 24,09</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 35,24</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-16,9; 13,43</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-74,02; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-57,23; 487,16</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-83,05; 216,21</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-1.148256470623242</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.155448186346194</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.167521693815905</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.9410066642790165</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3924060128583963</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2554269258948466</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.5102919676501351</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.7227663780648447</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>19,01</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-7,13</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-6,32</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-15,52</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>65,47%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-27,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-76,74%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.571716039407171</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.367016737318847</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.987659205576307</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.054483926718263</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8300515518224133</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6948335787731361</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.8205683240010098</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-17,97; 56,31</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-32,73; 0,0</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-35,34; 21,07</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-42,12; 0,98</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-43,02; 398,97</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 461,15</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.227798902011798</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.949199189453279</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.4762584568692798</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.516914186746677</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.176108386968562</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7450159678841205</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.3440070826739598</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +977,281 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,29%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-4,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-0,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>2.301357767939168</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.211668885279389</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3.524895956702501</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.3859787617746652</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>2.274835319656108</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.4965965249404438</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1167505876013339</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-7,34; 8,24</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-6,82; 5,97</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-7,93; 7,44</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-5,88; 6,79</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-39,22; 66,09</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-44,86; 66,51</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-44,35; 66,52</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-43,38; 91,64</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.1800223332387041</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.969777456722502</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.20208795944204</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.773702207012456</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.6244636173922369</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="n">
+        <v>-0.8384572686988715</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.151808692586084</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5.070810693497556</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>7.369622544097583</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.68340082209954</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="n">
+        <v>5.72431277704857</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="n">
+        <v>2.535889853705077</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.2553461702338534</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-1.343493959938817</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.2686485221950044</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-3.347337045641869</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.05615175230359878</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.07962585226514753</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.800921358299384</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-5.392973079172279</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-6.638395775115148</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-5.144385437341981</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-9.730206548492157</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.8224278851165382</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>5.53368784873259</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>5.709353733208493</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.1752928003401692</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>2.825830695852035</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.4440279204333163</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.1134233242811877</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.2515257417875019</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.01852942140691052</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.1420758275144762</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.04485248393340734</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.1059986258613462</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.007471025207381486</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.137783604370834</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.51872723233402</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.17207483878466</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-1.461593455562475</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.5434092635998952</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.4747974324083133</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.3958696906953683</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.4634032866384233</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.9919754636408007</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.239295375491677</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.678551188832297</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.665454437194806</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.4138645334097181</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.703664145476147</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1.009141670679074</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.9470953788572744</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1259,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
